--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129627810</v>
+        <v>129627881</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601932</v>
+        <v>601966</v>
       </c>
       <c r="R3" t="n">
-        <v>6978498</v>
+        <v>6978655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129627881</v>
+        <v>129627810</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601966</v>
+        <v>601932</v>
       </c>
       <c r="R4" t="n">
-        <v>6978655</v>
+        <v>6978498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B8" t="n">
-        <v>80178</v>
+        <v>82878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R8" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B9" t="n">
-        <v>82878</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R9" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627878</v>
+        <v>129627815</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601794</v>
+        <v>602026</v>
       </c>
       <c r="R26" t="n">
-        <v>6978568</v>
+        <v>6978671</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627815</v>
+        <v>129627878</v>
       </c>
       <c r="B27" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602026</v>
+        <v>601794</v>
       </c>
       <c r="R27" t="n">
-        <v>6978671</v>
+        <v>6978568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627870</v>
+        <v>129627831</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>82878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602039</v>
+        <v>601793</v>
       </c>
       <c r="R28" t="n">
-        <v>6978536</v>
+        <v>6978563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627867</v>
+        <v>129627870</v>
       </c>
       <c r="B29" t="n">
-        <v>97598</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601979</v>
+        <v>602039</v>
       </c>
       <c r="R29" t="n">
-        <v>6978701</v>
+        <v>6978536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627814</v>
+        <v>129627871</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601968</v>
+        <v>602019</v>
       </c>
       <c r="R30" t="n">
-        <v>6978566</v>
+        <v>6978525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,11 +3492,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627831</v>
+        <v>129627825</v>
       </c>
       <c r="B31" t="n">
-        <v>82878</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,21 +3529,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601793</v>
+        <v>601965</v>
       </c>
       <c r="R31" t="n">
-        <v>6978563</v>
+        <v>6978658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627871</v>
+        <v>129627819</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>80177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602019</v>
+        <v>601911</v>
       </c>
       <c r="R32" t="n">
-        <v>6978525</v>
+        <v>6978481</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627825</v>
+        <v>129627814</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,21 +3723,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601965</v>
+        <v>601968</v>
       </c>
       <c r="R33" t="n">
-        <v>6978658</v>
+        <v>6978566</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3788,6 +3783,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627819</v>
+        <v>129627867</v>
       </c>
       <c r="B34" t="n">
-        <v>80177</v>
+        <v>97598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601911</v>
+        <v>601979</v>
       </c>
       <c r="R34" t="n">
-        <v>6978481</v>
+        <v>6978701</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4300,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R39" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,11 +4371,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4402,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627827</v>
+        <v>129627879</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4437,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>602032</v>
+        <v>601900</v>
       </c>
       <c r="R40" t="n">
-        <v>6978549</v>
+        <v>6978557</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,7 +4472,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4504,32 +4499,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627817</v>
+        <v>129627827</v>
       </c>
       <c r="B41" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4539,10 +4534,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601963</v>
+        <v>602032</v>
       </c>
       <c r="R41" t="n">
-        <v>6978658</v>
+        <v>6978549</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,6 +4570,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627879</v>
+        <v>129627863</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4612,21 +4612,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601900</v>
+        <v>601836</v>
       </c>
       <c r="R42" t="n">
-        <v>6978557</v>
+        <v>6978478</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627809</v>
+        <v>129627828</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601974</v>
+        <v>602036</v>
       </c>
       <c r="R11" t="n">
-        <v>6978634</v>
+        <v>6978545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627828</v>
+        <v>129627809</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602036</v>
+        <v>601974</v>
       </c>
       <c r="R12" t="n">
-        <v>6978545</v>
+        <v>6978634</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627873</v>
+        <v>129627882</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602000</v>
+        <v>602018</v>
       </c>
       <c r="R14" t="n">
-        <v>6978519</v>
+        <v>6978681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,32 +1956,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627818</v>
+        <v>129627873</v>
       </c>
       <c r="B15" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601994</v>
+        <v>602000</v>
       </c>
       <c r="R15" t="n">
-        <v>6978517</v>
+        <v>6978519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627824</v>
+        <v>129627818</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601970</v>
+        <v>601994</v>
       </c>
       <c r="R16" t="n">
-        <v>6978601</v>
+        <v>6978517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627882</v>
+        <v>129627824</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602018</v>
+        <v>601970</v>
       </c>
       <c r="R17" t="n">
-        <v>6978681</v>
+        <v>6978601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,11 +2221,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627823</v>
+        <v>129627880</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601951</v>
+        <v>601908</v>
       </c>
       <c r="R20" t="n">
-        <v>6978564</v>
+        <v>6978584</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2512,6 +2512,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627880</v>
+        <v>129627823</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601908</v>
+        <v>601951</v>
       </c>
       <c r="R21" t="n">
-        <v>6978584</v>
+        <v>6978564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2609,11 +2614,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627815</v>
+        <v>129627878</v>
       </c>
       <c r="B26" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602026</v>
+        <v>601794</v>
       </c>
       <c r="R26" t="n">
-        <v>6978671</v>
+        <v>6978568</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627878</v>
+        <v>129627815</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601794</v>
+        <v>602026</v>
       </c>
       <c r="R27" t="n">
-        <v>6978568</v>
+        <v>6978671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627870</v>
+        <v>129627871</v>
       </c>
       <c r="B29" t="n">
         <v>80149</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602039</v>
+        <v>602019</v>
       </c>
       <c r="R29" t="n">
-        <v>6978536</v>
+        <v>6978525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627871</v>
+        <v>129627825</v>
       </c>
       <c r="B30" t="n">
         <v>80149</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602019</v>
+        <v>601965</v>
       </c>
       <c r="R30" t="n">
-        <v>6978525</v>
+        <v>6978658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627825</v>
+        <v>129627819</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601965</v>
+        <v>601911</v>
       </c>
       <c r="R31" t="n">
-        <v>6978658</v>
+        <v>6978481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627819</v>
+        <v>129627814</v>
       </c>
       <c r="B32" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601911</v>
+        <v>601968</v>
       </c>
       <c r="R32" t="n">
-        <v>6978481</v>
+        <v>6978566</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3686,6 +3686,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3712,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627814</v>
+        <v>129627870</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3723,21 +3728,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601968</v>
+        <v>602039</v>
       </c>
       <c r="R33" t="n">
-        <v>6978566</v>
+        <v>6978536</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3783,11 +3788,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4300,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627817</v>
+        <v>129627863</v>
       </c>
       <c r="B39" t="n">
-        <v>80178</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601963</v>
+        <v>601836</v>
       </c>
       <c r="R39" t="n">
-        <v>6978658</v>
+        <v>6978478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,6 +4371,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4397,32 +4402,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627879</v>
+        <v>129627817</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4437,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601900</v>
+        <v>601963</v>
       </c>
       <c r="R40" t="n">
-        <v>6978557</v>
+        <v>6978658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,11 +4473,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627863</v>
+        <v>129627879</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4612,21 +4612,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601836</v>
+        <v>601900</v>
       </c>
       <c r="R42" t="n">
-        <v>6978478</v>
+        <v>6978557</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,6 +4700,103 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129627808</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91777</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Malstrandsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>601912</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6978477</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129627877</v>
+        <v>129627810</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601809</v>
+        <v>601932</v>
       </c>
       <c r="R2" t="n">
-        <v>6978509</v>
+        <v>6978498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129627881</v>
+        <v>129627877</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601966</v>
+        <v>601809</v>
       </c>
       <c r="R3" t="n">
-        <v>6978655</v>
+        <v>6978509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129627810</v>
+        <v>129627881</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601932</v>
+        <v>601966</v>
       </c>
       <c r="R4" t="n">
-        <v>6978498</v>
+        <v>6978655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B8" t="n">
-        <v>82878</v>
+        <v>80178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R8" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>82878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R9" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627828</v>
+        <v>129627809</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>602036</v>
+        <v>601974</v>
       </c>
       <c r="R11" t="n">
-        <v>6978545</v>
+        <v>6978634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627809</v>
+        <v>129627828</v>
       </c>
       <c r="B12" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601974</v>
+        <v>602036</v>
       </c>
       <c r="R12" t="n">
-        <v>6978634</v>
+        <v>6978545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627882</v>
+        <v>129627873</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602018</v>
+        <v>602000</v>
       </c>
       <c r="R14" t="n">
-        <v>6978681</v>
+        <v>6978519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627873</v>
+        <v>129627824</v>
       </c>
       <c r="B15" t="n">
         <v>80149</v>
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602000</v>
+        <v>601970</v>
       </c>
       <c r="R15" t="n">
-        <v>6978519</v>
+        <v>6978601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627818</v>
+        <v>129627882</v>
       </c>
       <c r="B16" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601994</v>
+        <v>602018</v>
       </c>
       <c r="R16" t="n">
-        <v>6978517</v>
+        <v>6978681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,7 +2150,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627824</v>
+        <v>129627869</v>
       </c>
       <c r="B17" t="n">
         <v>80149</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601970</v>
+        <v>602056</v>
       </c>
       <c r="R17" t="n">
-        <v>6978601</v>
+        <v>6978555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627869</v>
+        <v>129627818</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602056</v>
+        <v>601994</v>
       </c>
       <c r="R18" t="n">
-        <v>6978555</v>
+        <v>6978517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627880</v>
+        <v>129627823</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601908</v>
+        <v>601951</v>
       </c>
       <c r="R20" t="n">
-        <v>6978584</v>
+        <v>6978564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2512,11 +2512,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627823</v>
+        <v>129627880</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601951</v>
+        <v>601908</v>
       </c>
       <c r="R21" t="n">
-        <v>6978564</v>
+        <v>6978584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,6 +2609,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3324,7 +3324,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627871</v>
+        <v>129627870</v>
       </c>
       <c r="B29" t="n">
         <v>80149</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602019</v>
+        <v>602039</v>
       </c>
       <c r="R29" t="n">
-        <v>6978525</v>
+        <v>6978536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627825</v>
+        <v>129627871</v>
       </c>
       <c r="B30" t="n">
         <v>80149</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601965</v>
+        <v>602019</v>
       </c>
       <c r="R30" t="n">
-        <v>6978658</v>
+        <v>6978525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627819</v>
+        <v>129627825</v>
       </c>
       <c r="B31" t="n">
-        <v>80177</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601911</v>
+        <v>601965</v>
       </c>
       <c r="R31" t="n">
-        <v>6978481</v>
+        <v>6978658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627814</v>
+        <v>129627819</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601968</v>
+        <v>601911</v>
       </c>
       <c r="R32" t="n">
-        <v>6978566</v>
+        <v>6978481</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3686,11 +3686,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3717,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627870</v>
+        <v>129627814</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,21 +3723,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602039</v>
+        <v>601968</v>
       </c>
       <c r="R33" t="n">
-        <v>6978536</v>
+        <v>6978566</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3788,6 +3783,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3911,34 +3911,30 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B35" t="n">
-        <v>97598</v>
+        <v>91573</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3946,10 +3942,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R35" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,6 +3978,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4008,30 +4009,34 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B36" t="n">
-        <v>91573</v>
+        <v>97598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4039,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R36" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,11 +4080,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4300,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R39" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,11 +4371,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4402,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627817</v>
+        <v>129627827</v>
       </c>
       <c r="B40" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4437,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601963</v>
+        <v>602032</v>
       </c>
       <c r="R40" t="n">
-        <v>6978658</v>
+        <v>6978549</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,6 +4468,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4499,32 +4499,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627827</v>
+        <v>129627879</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602032</v>
+        <v>601900</v>
       </c>
       <c r="R41" t="n">
-        <v>6978549</v>
+        <v>6978557</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627879</v>
+        <v>129627863</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4612,21 +4612,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601900</v>
+        <v>601836</v>
       </c>
       <c r="R42" t="n">
-        <v>6978557</v>
+        <v>6978478</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129627810</v>
+        <v>129627877</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601932</v>
+        <v>601809</v>
       </c>
       <c r="R2" t="n">
-        <v>6978498</v>
+        <v>6978509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129627877</v>
+        <v>129627881</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601809</v>
+        <v>601966</v>
       </c>
       <c r="R3" t="n">
-        <v>6978509</v>
+        <v>6978655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129627881</v>
+        <v>129627810</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601966</v>
+        <v>601932</v>
       </c>
       <c r="R4" t="n">
-        <v>6978655</v>
+        <v>6978498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>129627874</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129627872</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129627865</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129627816</v>
       </c>
       <c r="B8" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129627830</v>
       </c>
       <c r="B9" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129627822</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627809</v>
+        <v>129627828</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601974</v>
+        <v>602036</v>
       </c>
       <c r="R11" t="n">
-        <v>6978634</v>
+        <v>6978545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627828</v>
+        <v>129627809</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602036</v>
+        <v>601974</v>
       </c>
       <c r="R12" t="n">
-        <v>6978545</v>
+        <v>6978634</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,7 +1760,7 @@
         <v>129627820</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129627873</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627824</v>
+        <v>129627818</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80204</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601970</v>
+        <v>601994</v>
       </c>
       <c r="R15" t="n">
-        <v>6978601</v>
+        <v>6978517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
         <v>129627882</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627869</v>
+        <v>129627824</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602056</v>
+        <v>601970</v>
       </c>
       <c r="R17" t="n">
-        <v>6978555</v>
+        <v>6978601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627818</v>
+        <v>129627869</v>
       </c>
       <c r="B18" t="n">
-        <v>80178</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601994</v>
+        <v>602056</v>
       </c>
       <c r="R18" t="n">
-        <v>6978517</v>
+        <v>6978555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2347,7 +2347,7 @@
         <v>129627829</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129627823</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627880</v>
+        <v>129627868</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601908</v>
+        <v>602022</v>
       </c>
       <c r="R21" t="n">
-        <v>6978584</v>
+        <v>6978574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2609,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2640,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627868</v>
+        <v>129627880</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602022</v>
+        <v>601908</v>
       </c>
       <c r="R22" t="n">
-        <v>6978574</v>
+        <v>6978584</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,6 +2706,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2740,7 +2740,7 @@
         <v>129627876</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>129627859</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>129627832</v>
       </c>
       <c r="B25" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129627878</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>129627815</v>
       </c>
       <c r="B27" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627831</v>
+        <v>129627867</v>
       </c>
       <c r="B28" t="n">
-        <v>82878</v>
+        <v>97627</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601793</v>
+        <v>601979</v>
       </c>
       <c r="R28" t="n">
-        <v>6978563</v>
+        <v>6978701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
         <v>129627870</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627871</v>
+        <v>129627825</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602019</v>
+        <v>601965</v>
       </c>
       <c r="R30" t="n">
-        <v>6978525</v>
+        <v>6978658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627825</v>
+        <v>129627871</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601965</v>
+        <v>602019</v>
       </c>
       <c r="R31" t="n">
-        <v>6978658</v>
+        <v>6978525</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>129627819</v>
       </c>
       <c r="B32" t="n">
-        <v>80177</v>
+        <v>80203</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627814</v>
+        <v>129627831</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>82905</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601968</v>
+        <v>601793</v>
       </c>
       <c r="R33" t="n">
-        <v>6978566</v>
+        <v>6978563</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3783,11 +3783,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3814,32 +3809,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627867</v>
+        <v>129627814</v>
       </c>
       <c r="B34" t="n">
-        <v>97598</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601979</v>
+        <v>601968</v>
       </c>
       <c r="R34" t="n">
-        <v>6978701</v>
+        <v>6978566</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,6 +3880,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3914,7 +3914,7 @@
         <v>129627875</v>
       </c>
       <c r="B35" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>129627864</v>
       </c>
       <c r="B36" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4106,32 +4106,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627826</v>
+        <v>129627834</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>80210</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601982</v>
+        <v>601971</v>
       </c>
       <c r="R37" t="n">
-        <v>6978637</v>
+        <v>6978654</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4203,32 +4203,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627834</v>
+        <v>129627826</v>
       </c>
       <c r="B38" t="n">
-        <v>80184</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601971</v>
+        <v>601982</v>
       </c>
       <c r="R38" t="n">
-        <v>6978654</v>
+        <v>6978637</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4303,7 +4303,7 @@
         <v>129627817</v>
       </c>
       <c r="B39" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4397,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627827</v>
+        <v>129627879</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>602032</v>
+        <v>601900</v>
       </c>
       <c r="R40" t="n">
-        <v>6978549</v>
+        <v>6978557</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627879</v>
+        <v>129627863</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57890</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601900</v>
+        <v>601836</v>
       </c>
       <c r="R41" t="n">
-        <v>6978557</v>
+        <v>6978478</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4601,32 +4601,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627863</v>
+        <v>129627827</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>98756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601836</v>
+        <v>602032</v>
       </c>
       <c r="R42" t="n">
-        <v>6978478</v>
+        <v>6978549</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4706,7 +4706,7 @@
         <v>129627808</v>
       </c>
       <c r="B43" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627828</v>
+        <v>129627809</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>602036</v>
+        <v>601974</v>
       </c>
       <c r="R11" t="n">
-        <v>6978545</v>
+        <v>6978634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627809</v>
+        <v>129627828</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601974</v>
+        <v>602036</v>
       </c>
       <c r="R12" t="n">
-        <v>6978634</v>
+        <v>6978545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3911,30 +3911,34 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B35" t="n">
-        <v>91601</v>
+        <v>97627</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3942,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R35" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3978,11 +3982,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4009,34 +4008,30 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B36" t="n">
-        <v>97627</v>
+        <v>91601</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4044,10 +4039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R36" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4080,6 +4075,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4300,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627817</v>
+        <v>129627863</v>
       </c>
       <c r="B39" t="n">
-        <v>80204</v>
+        <v>57890</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601963</v>
+        <v>601836</v>
       </c>
       <c r="R39" t="n">
-        <v>6978658</v>
+        <v>6978478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,6 +4371,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4397,32 +4402,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627879</v>
+        <v>129627817</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>80204</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4437,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601900</v>
+        <v>601963</v>
       </c>
       <c r="R40" t="n">
-        <v>6978557</v>
+        <v>6978658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,11 +4473,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627863</v>
+        <v>129627879</v>
       </c>
       <c r="B41" t="n">
-        <v>57890</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601836</v>
+        <v>601900</v>
       </c>
       <c r="R41" t="n">
-        <v>6978478</v>
+        <v>6978557</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627877</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129627881</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129627810</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129627874</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129627872</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129627865</v>
       </c>
       <c r="B7" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B8" t="n">
-        <v>80204</v>
+        <v>82910</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R8" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B9" t="n">
-        <v>82905</v>
+        <v>80209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R9" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
         <v>129627822</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129627809</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129627828</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129627820</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627873</v>
+        <v>129627882</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602000</v>
+        <v>602018</v>
       </c>
       <c r="R14" t="n">
-        <v>6978519</v>
+        <v>6978681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,32 +1956,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627818</v>
+        <v>129627873</v>
       </c>
       <c r="B15" t="n">
-        <v>80204</v>
+        <v>80180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601994</v>
+        <v>602000</v>
       </c>
       <c r="R15" t="n">
-        <v>6978517</v>
+        <v>6978519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627882</v>
+        <v>129627818</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>80209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602018</v>
+        <v>601994</v>
       </c>
       <c r="R16" t="n">
-        <v>6978681</v>
+        <v>6978517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,11 +2124,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2153,7 +2153,7 @@
         <v>129627824</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129627869</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>129627829</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129627823</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129627868</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129627880</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>129627876</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>129627859</v>
       </c>
       <c r="B24" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>129627832</v>
       </c>
       <c r="B25" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627878</v>
+        <v>129627815</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>91608</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601794</v>
+        <v>602026</v>
       </c>
       <c r="R26" t="n">
-        <v>6978568</v>
+        <v>6978671</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627815</v>
+        <v>129627878</v>
       </c>
       <c r="B27" t="n">
-        <v>91602</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602026</v>
+        <v>601794</v>
       </c>
       <c r="R27" t="n">
-        <v>6978671</v>
+        <v>6978568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>129627867</v>
       </c>
       <c r="B28" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627870</v>
+        <v>129627831</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>82910</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602039</v>
+        <v>601793</v>
       </c>
       <c r="R29" t="n">
-        <v>6978536</v>
+        <v>6978563</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627825</v>
+        <v>129627870</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601965</v>
+        <v>602039</v>
       </c>
       <c r="R30" t="n">
-        <v>6978658</v>
+        <v>6978536</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627871</v>
+        <v>129627825</v>
       </c>
       <c r="B31" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602019</v>
+        <v>601965</v>
       </c>
       <c r="R31" t="n">
-        <v>6978525</v>
+        <v>6978658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627819</v>
+        <v>129627871</v>
       </c>
       <c r="B32" t="n">
-        <v>80203</v>
+        <v>80180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601911</v>
+        <v>602019</v>
       </c>
       <c r="R32" t="n">
-        <v>6978481</v>
+        <v>6978525</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3712,32 +3712,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627831</v>
+        <v>129627819</v>
       </c>
       <c r="B33" t="n">
-        <v>82905</v>
+        <v>80208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601793</v>
+        <v>601911</v>
       </c>
       <c r="R33" t="n">
-        <v>6978563</v>
+        <v>6978481</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3812,7 +3812,7 @@
         <v>129627814</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>129627864</v>
       </c>
       <c r="B35" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>129627875</v>
       </c>
       <c r="B36" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>129627834</v>
       </c>
       <c r="B37" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>129627826</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4300,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B39" t="n">
-        <v>57890</v>
+        <v>80209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R39" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,11 +4371,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4402,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627817</v>
+        <v>129627879</v>
       </c>
       <c r="B40" t="n">
-        <v>80204</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4437,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601963</v>
+        <v>601900</v>
       </c>
       <c r="R40" t="n">
-        <v>6978658</v>
+        <v>6978557</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,6 +4468,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4499,10 +4499,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627879</v>
+        <v>129627863</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>57895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601900</v>
+        <v>601836</v>
       </c>
       <c r="R41" t="n">
-        <v>6978557</v>
+        <v>6978478</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4604,7 +4604,7 @@
         <v>129627827</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129627808</v>
       </c>
       <c r="B43" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627877</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129627881</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129627810</v>
+        <v>129627874</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601932</v>
+        <v>601945</v>
       </c>
       <c r="R4" t="n">
-        <v>6978498</v>
+        <v>6978600</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Cs 250 stycken 15 blommstänger ( utblommade)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627874</v>
+        <v>129627865</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>97640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601945</v>
+        <v>601941</v>
       </c>
       <c r="R5" t="n">
-        <v>6978600</v>
+        <v>6978598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cs 250 stycken 15 blommstänger ( utblommade)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1071,7 @@
         <v>129627872</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627865</v>
+        <v>129627830</v>
       </c>
       <c r="B7" t="n">
-        <v>97639</v>
+        <v>82911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601941</v>
+        <v>601964</v>
       </c>
       <c r="R7" t="n">
-        <v>6978598</v>
+        <v>6978529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B8" t="n">
-        <v>82910</v>
+        <v>80210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R8" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627816</v>
+        <v>129627822</v>
       </c>
       <c r="B9" t="n">
-        <v>80209</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602018</v>
+        <v>601929</v>
       </c>
       <c r="R9" t="n">
-        <v>6978523</v>
+        <v>6978510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627822</v>
+        <v>129627828</v>
       </c>
       <c r="B10" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601929</v>
+        <v>602036</v>
       </c>
       <c r="R10" t="n">
-        <v>6978510</v>
+        <v>6978545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1561,7 @@
         <v>129627809</v>
       </c>
       <c r="B11" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627828</v>
+        <v>129627820</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602036</v>
+        <v>602038</v>
       </c>
       <c r="R12" t="n">
-        <v>6978545</v>
+        <v>6978539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1726,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627820</v>
+        <v>129627818</v>
       </c>
       <c r="B13" t="n">
-        <v>80180</v>
+        <v>80210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602038</v>
+        <v>601994</v>
       </c>
       <c r="R13" t="n">
-        <v>6978539</v>
+        <v>6978517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627882</v>
+        <v>129627824</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602018</v>
+        <v>601970</v>
       </c>
       <c r="R14" t="n">
-        <v>6978681</v>
+        <v>6978601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1920,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1959,7 +1949,7 @@
         <v>129627873</v>
       </c>
       <c r="B15" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627818</v>
+        <v>129627882</v>
       </c>
       <c r="B16" t="n">
-        <v>80209</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601994</v>
+        <v>602018</v>
       </c>
       <c r="R16" t="n">
-        <v>6978517</v>
+        <v>6978681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,6 +2114,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627824</v>
+        <v>129627869</v>
       </c>
       <c r="B17" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601970</v>
+        <v>602056</v>
       </c>
       <c r="R17" t="n">
-        <v>6978601</v>
+        <v>6978555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627869</v>
+        <v>129627829</v>
       </c>
       <c r="B18" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602056</v>
+        <v>601968</v>
       </c>
       <c r="R18" t="n">
-        <v>6978555</v>
+        <v>6978544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627829</v>
+        <v>129627880</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601968</v>
+        <v>601908</v>
       </c>
       <c r="R19" t="n">
-        <v>6978544</v>
+        <v>6978584</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627823</v>
+        <v>129627868</v>
       </c>
       <c r="B20" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601951</v>
+        <v>602022</v>
       </c>
       <c r="R20" t="n">
-        <v>6978564</v>
+        <v>6978574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627868</v>
+        <v>129627823</v>
       </c>
       <c r="B21" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602022</v>
+        <v>601951</v>
       </c>
       <c r="R21" t="n">
-        <v>6978574</v>
+        <v>6978564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627880</v>
+        <v>129627876</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601908</v>
+        <v>602043</v>
       </c>
       <c r="R22" t="n">
-        <v>6978584</v>
+        <v>6978580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,27 +2732,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129627876</v>
+        <v>129627832</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>80216</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>602043</v>
+        <v>601930</v>
       </c>
       <c r="R23" t="n">
-        <v>6978580</v>
+        <v>6978509</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627859</v>
+        <v>129627815</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>91609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>602072</v>
+        <v>602026</v>
       </c>
       <c r="R24" t="n">
-        <v>6978533</v>
+        <v>6978671</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,11 +2900,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2936,27 +2926,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129627832</v>
+        <v>129627878</v>
       </c>
       <c r="B25" t="n">
-        <v>80215</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2971,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601930</v>
+        <v>601794</v>
       </c>
       <c r="R25" t="n">
-        <v>6978509</v>
+        <v>6978568</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627815</v>
+        <v>129627831</v>
       </c>
       <c r="B26" t="n">
-        <v>91608</v>
+        <v>82911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602026</v>
+        <v>601793</v>
       </c>
       <c r="R26" t="n">
-        <v>6978671</v>
+        <v>6978563</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627878</v>
+        <v>129627870</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601794</v>
+        <v>602039</v>
       </c>
       <c r="R27" t="n">
-        <v>6978568</v>
+        <v>6978536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,32 +3217,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627867</v>
+        <v>129627825</v>
       </c>
       <c r="B28" t="n">
-        <v>97639</v>
+        <v>80181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601979</v>
+        <v>601965</v>
       </c>
       <c r="R28" t="n">
-        <v>6978701</v>
+        <v>6978658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627831</v>
+        <v>129627871</v>
       </c>
       <c r="B29" t="n">
-        <v>82910</v>
+        <v>80181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601793</v>
+        <v>602019</v>
       </c>
       <c r="R29" t="n">
-        <v>6978563</v>
+        <v>6978525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627870</v>
+        <v>129627819</v>
       </c>
       <c r="B30" t="n">
-        <v>80180</v>
+        <v>80209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602039</v>
+        <v>601911</v>
       </c>
       <c r="R30" t="n">
-        <v>6978536</v>
+        <v>6978481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,32 +3508,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627825</v>
+        <v>129627867</v>
       </c>
       <c r="B31" t="n">
-        <v>80180</v>
+        <v>97640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601965</v>
+        <v>601979</v>
       </c>
       <c r="R31" t="n">
-        <v>6978658</v>
+        <v>6978701</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,32 +3605,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627871</v>
+        <v>129627864</v>
       </c>
       <c r="B32" t="n">
-        <v>80180</v>
+        <v>97640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602019</v>
+        <v>602045</v>
       </c>
       <c r="R32" t="n">
-        <v>6978525</v>
+        <v>6978541</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3712,34 +3702,30 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627819</v>
+        <v>129627875</v>
       </c>
       <c r="B33" t="n">
-        <v>80208</v>
+        <v>91608</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3747,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601911</v>
+        <v>601812</v>
       </c>
       <c r="R33" t="n">
-        <v>6978481</v>
+        <v>6978576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3783,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3809,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627814</v>
+        <v>129627826</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3820,21 +3811,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3844,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601968</v>
+        <v>601982</v>
       </c>
       <c r="R34" t="n">
-        <v>6978566</v>
+        <v>6978637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3880,11 +3871,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3911,10 +3897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627864</v>
+        <v>129627834</v>
       </c>
       <c r="B35" t="n">
-        <v>97639</v>
+        <v>80216</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,21 +3908,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602045</v>
+        <v>601971</v>
       </c>
       <c r="R35" t="n">
-        <v>6978541</v>
+        <v>6978654</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4008,30 +3994,34 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627875</v>
+        <v>129627827</v>
       </c>
       <c r="B36" t="n">
-        <v>91607</v>
+        <v>98769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4039,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601812</v>
+        <v>602032</v>
       </c>
       <c r="R36" t="n">
-        <v>6978576</v>
+        <v>6978549</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,7 +4069,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Stora fina exemplar på gran.</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4106,32 +4096,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627834</v>
+        <v>129627863</v>
       </c>
       <c r="B37" t="n">
-        <v>80215</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4141,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601971</v>
+        <v>601836</v>
       </c>
       <c r="R37" t="n">
-        <v>6978654</v>
+        <v>6978478</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4177,6 +4167,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4203,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627826</v>
+        <v>129627879</v>
       </c>
       <c r="B38" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4214,21 +4209,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4238,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601982</v>
+        <v>601900</v>
       </c>
       <c r="R38" t="n">
-        <v>6978637</v>
+        <v>6978557</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4274,6 +4269,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4303,7 +4303,7 @@
         <v>129627817</v>
       </c>
       <c r="B39" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4397,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627879</v>
+        <v>129627808</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>91812</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1106</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601900</v>
+        <v>601912</v>
       </c>
       <c r="R40" t="n">
-        <v>6978557</v>
+        <v>6978477</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,11 +4468,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4499,10 +4494,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627863</v>
+        <v>129627810</v>
       </c>
       <c r="B41" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4510,21 +4505,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4534,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601836</v>
+        <v>601932</v>
       </c>
       <c r="R41" t="n">
-        <v>6978478</v>
+        <v>6978498</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4574,7 +4569,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4601,32 +4596,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627827</v>
+        <v>129627859</v>
       </c>
       <c r="B42" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4636,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602032</v>
+        <v>602072</v>
       </c>
       <c r="R42" t="n">
-        <v>6978549</v>
+        <v>6978533</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4676,7 +4671,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>Äldre ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4703,32 +4698,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627808</v>
+        <v>129627814</v>
       </c>
       <c r="B43" t="n">
-        <v>91811</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4738,10 +4733,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601912</v>
+        <v>601968</v>
       </c>
       <c r="R43" t="n">
-        <v>6978477</v>
+        <v>6978566</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4774,6 +4769,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627818</v>
+        <v>129627873</v>
       </c>
       <c r="B13" t="n">
-        <v>80210</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601994</v>
+        <v>602000</v>
       </c>
       <c r="R13" t="n">
-        <v>6978517</v>
+        <v>6978519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627824</v>
+        <v>129627882</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601970</v>
+        <v>602018</v>
       </c>
       <c r="R14" t="n">
-        <v>6978601</v>
+        <v>6978681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1920,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627873</v>
+        <v>129627869</v>
       </c>
       <c r="B15" t="n">
         <v>80181</v>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602000</v>
+        <v>602056</v>
       </c>
       <c r="R15" t="n">
-        <v>6978519</v>
+        <v>6978555</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627882</v>
+        <v>129627818</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>80210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602018</v>
+        <v>601994</v>
       </c>
       <c r="R16" t="n">
-        <v>6978681</v>
+        <v>6978517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2114,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,7 +2145,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627869</v>
+        <v>129627824</v>
       </c>
       <c r="B17" t="n">
         <v>80181</v>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602056</v>
+        <v>601970</v>
       </c>
       <c r="R17" t="n">
-        <v>6978555</v>
+        <v>6978601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3120,32 +3120,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627870</v>
+        <v>129627867</v>
       </c>
       <c r="B27" t="n">
-        <v>80181</v>
+        <v>97640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602039</v>
+        <v>601979</v>
       </c>
       <c r="R27" t="n">
-        <v>6978536</v>
+        <v>6978701</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627825</v>
+        <v>129627870</v>
       </c>
       <c r="B28" t="n">
         <v>80181</v>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601965</v>
+        <v>602039</v>
       </c>
       <c r="R28" t="n">
-        <v>6978658</v>
+        <v>6978536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627871</v>
+        <v>129627825</v>
       </c>
       <c r="B29" t="n">
         <v>80181</v>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602019</v>
+        <v>601965</v>
       </c>
       <c r="R29" t="n">
-        <v>6978525</v>
+        <v>6978658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627819</v>
+        <v>129627871</v>
       </c>
       <c r="B30" t="n">
-        <v>80209</v>
+        <v>80181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601911</v>
+        <v>602019</v>
       </c>
       <c r="R30" t="n">
-        <v>6978481</v>
+        <v>6978525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627867</v>
+        <v>129627819</v>
       </c>
       <c r="B31" t="n">
-        <v>97640</v>
+        <v>80209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601979</v>
+        <v>601911</v>
       </c>
       <c r="R31" t="n">
-        <v>6978701</v>
+        <v>6978481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,34 +3605,30 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B32" t="n">
-        <v>97640</v>
+        <v>91608</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3640,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R32" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,6 +3672,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3702,30 +3703,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B33" t="n">
-        <v>91608</v>
+        <v>97640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R33" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627827</v>
+        <v>129627879</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602032</v>
+        <v>601900</v>
       </c>
       <c r="R36" t="n">
-        <v>6978549</v>
+        <v>6978557</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,32 +4096,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>80210</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R37" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,11 +4167,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4198,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627879</v>
+        <v>129627863</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601900</v>
+        <v>601836</v>
       </c>
       <c r="R38" t="n">
-        <v>6978557</v>
+        <v>6978478</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4273,7 +4268,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4300,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627817</v>
+        <v>129627827</v>
       </c>
       <c r="B39" t="n">
-        <v>80210</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601963</v>
+        <v>602032</v>
       </c>
       <c r="R39" t="n">
-        <v>6978658</v>
+        <v>6978549</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,6 +4366,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4397,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627808</v>
+        <v>129627810</v>
       </c>
       <c r="B40" t="n">
-        <v>91812</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601912</v>
+        <v>601932</v>
       </c>
       <c r="R40" t="n">
-        <v>6978477</v>
+        <v>6978498</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,6 +4468,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4494,7 +4499,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627810</v>
+        <v>129627859</v>
       </c>
       <c r="B41" t="n">
         <v>57736</v>
@@ -4529,10 +4534,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601932</v>
+        <v>602072</v>
       </c>
       <c r="R41" t="n">
-        <v>6978498</v>
+        <v>6978533</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4569,7 +4574,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4596,7 +4601,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627859</v>
+        <v>129627814</v>
       </c>
       <c r="B42" t="n">
         <v>57736</v>
@@ -4631,10 +4636,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602072</v>
+        <v>601968</v>
       </c>
       <c r="R42" t="n">
-        <v>6978533</v>
+        <v>6978566</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4671,7 +4676,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett</t>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4698,32 +4703,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627814</v>
+        <v>129627808</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>91817</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4733,10 +4738,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601968</v>
+        <v>601912</v>
       </c>
       <c r="R43" t="n">
-        <v>6978566</v>
+        <v>6978477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,11 +4774,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627877</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129627881</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129627874</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627865</v>
+        <v>129627872</v>
       </c>
       <c r="B5" t="n">
-        <v>97640</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601941</v>
+        <v>602013</v>
       </c>
       <c r="R5" t="n">
-        <v>6978598</v>
+        <v>6978512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627872</v>
+        <v>129627865</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>97645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602013</v>
+        <v>601941</v>
       </c>
       <c r="R6" t="n">
-        <v>6978512</v>
+        <v>6978598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B7" t="n">
-        <v>82911</v>
+        <v>80215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R7" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B8" t="n">
-        <v>80210</v>
+        <v>82916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R8" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>129627822</v>
       </c>
       <c r="B9" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129627828</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129627809</v>
       </c>
       <c r="B11" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129627820</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627873</v>
+        <v>129627882</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602000</v>
+        <v>602018</v>
       </c>
       <c r="R13" t="n">
-        <v>6978519</v>
+        <v>6978681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627882</v>
+        <v>129627824</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602018</v>
+        <v>601970</v>
       </c>
       <c r="R14" t="n">
-        <v>6978681</v>
+        <v>6978601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1954,7 +1954,7 @@
         <v>129627869</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627818</v>
+        <v>129627873</v>
       </c>
       <c r="B16" t="n">
-        <v>80210</v>
+        <v>80186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601994</v>
+        <v>602000</v>
       </c>
       <c r="R16" t="n">
-        <v>6978517</v>
+        <v>6978519</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627824</v>
+        <v>129627818</v>
       </c>
       <c r="B17" t="n">
-        <v>80181</v>
+        <v>80215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601970</v>
+        <v>601994</v>
       </c>
       <c r="R17" t="n">
-        <v>6978601</v>
+        <v>6978517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>129627829</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627880</v>
+        <v>129627823</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601908</v>
+        <v>601951</v>
       </c>
       <c r="R19" t="n">
-        <v>6978584</v>
+        <v>6978564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2410,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2444,7 +2439,7 @@
         <v>129627868</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627823</v>
+        <v>129627880</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601951</v>
+        <v>601908</v>
       </c>
       <c r="R21" t="n">
-        <v>6978564</v>
+        <v>6978584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2609,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2638,7 +2638,7 @@
         <v>129627876</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129627832</v>
       </c>
       <c r="B23" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>129627815</v>
       </c>
       <c r="B24" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129627878</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>129627831</v>
       </c>
       <c r="B26" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3120,32 +3120,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627867</v>
+        <v>129627870</v>
       </c>
       <c r="B27" t="n">
-        <v>97640</v>
+        <v>80186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601979</v>
+        <v>602039</v>
       </c>
       <c r="R27" t="n">
-        <v>6978701</v>
+        <v>6978536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627870</v>
+        <v>129627871</v>
       </c>
       <c r="B28" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602039</v>
+        <v>602019</v>
       </c>
       <c r="R28" t="n">
-        <v>6978536</v>
+        <v>6978525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3317,7 +3317,7 @@
         <v>129627825</v>
       </c>
       <c r="B29" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627871</v>
+        <v>129627819</v>
       </c>
       <c r="B30" t="n">
-        <v>80181</v>
+        <v>80214</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602019</v>
+        <v>601911</v>
       </c>
       <c r="R30" t="n">
-        <v>6978525</v>
+        <v>6978481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627819</v>
+        <v>129627867</v>
       </c>
       <c r="B31" t="n">
-        <v>80209</v>
+        <v>97645</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601911</v>
+        <v>601979</v>
       </c>
       <c r="R31" t="n">
-        <v>6978481</v>
+        <v>6978701</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,7 +3608,7 @@
         <v>129627875</v>
       </c>
       <c r="B32" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>129627864</v>
       </c>
       <c r="B33" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>129627826</v>
       </c>
       <c r="B34" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>129627834</v>
       </c>
       <c r="B35" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627879</v>
+        <v>129627817</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>80215</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601900</v>
+        <v>601963</v>
       </c>
       <c r="R36" t="n">
-        <v>6978557</v>
+        <v>6978658</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4065,11 +4065,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627817</v>
+        <v>129627827</v>
       </c>
       <c r="B37" t="n">
-        <v>80210</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4131,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601963</v>
+        <v>602032</v>
       </c>
       <c r="R37" t="n">
-        <v>6978658</v>
+        <v>6978549</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,6 +4162,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627863</v>
+        <v>129627879</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601836</v>
+        <v>601900</v>
       </c>
       <c r="R38" t="n">
-        <v>6978478</v>
+        <v>6978557</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4295,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627827</v>
+        <v>129627863</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602032</v>
+        <v>601836</v>
       </c>
       <c r="R39" t="n">
-        <v>6978549</v>
+        <v>6978478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627872</v>
+        <v>129627865</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>97645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602013</v>
+        <v>601941</v>
       </c>
       <c r="R5" t="n">
-        <v>6978512</v>
+        <v>6978598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627865</v>
+        <v>129627872</v>
       </c>
       <c r="B6" t="n">
-        <v>97645</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601941</v>
+        <v>602013</v>
       </c>
       <c r="R6" t="n">
-        <v>6978598</v>
+        <v>6978512</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B7" t="n">
-        <v>80215</v>
+        <v>82916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R7" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B8" t="n">
-        <v>82916</v>
+        <v>80215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R8" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627828</v>
+        <v>129627809</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602036</v>
+        <v>601974</v>
       </c>
       <c r="R10" t="n">
-        <v>6978545</v>
+        <v>6978634</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627809</v>
+        <v>129627828</v>
       </c>
       <c r="B11" t="n">
-        <v>91557</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601974</v>
+        <v>602036</v>
       </c>
       <c r="R11" t="n">
-        <v>6978634</v>
+        <v>6978545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627882</v>
+        <v>129627818</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602018</v>
+        <v>601994</v>
       </c>
       <c r="R13" t="n">
-        <v>6978681</v>
+        <v>6978517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,7 +1849,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627824</v>
+        <v>129627873</v>
       </c>
       <c r="B14" t="n">
         <v>80186</v>
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601970</v>
+        <v>602000</v>
       </c>
       <c r="R14" t="n">
-        <v>6978601</v>
+        <v>6978519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1946,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627869</v>
+        <v>129627824</v>
       </c>
       <c r="B15" t="n">
         <v>80186</v>
@@ -1986,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602056</v>
+        <v>601970</v>
       </c>
       <c r="R15" t="n">
-        <v>6978555</v>
+        <v>6978601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627873</v>
+        <v>129627882</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602000</v>
+        <v>602018</v>
       </c>
       <c r="R16" t="n">
-        <v>6978519</v>
+        <v>6978681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2114,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627818</v>
+        <v>129627869</v>
       </c>
       <c r="B17" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601994</v>
+        <v>602056</v>
       </c>
       <c r="R17" t="n">
-        <v>6978517</v>
+        <v>6978555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627868</v>
+        <v>129627880</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602022</v>
+        <v>601908</v>
       </c>
       <c r="R20" t="n">
-        <v>6978574</v>
+        <v>6978584</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2507,6 +2507,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2533,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627880</v>
+        <v>129627868</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601908</v>
+        <v>602022</v>
       </c>
       <c r="R21" t="n">
-        <v>6978584</v>
+        <v>6978574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2604,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627827</v>
+        <v>129627879</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602032</v>
+        <v>601900</v>
       </c>
       <c r="R37" t="n">
-        <v>6978549</v>
+        <v>6978557</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627879</v>
+        <v>129627863</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601900</v>
+        <v>601836</v>
       </c>
       <c r="R38" t="n">
-        <v>6978557</v>
+        <v>6978478</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4295,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627863</v>
+        <v>129627827</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601836</v>
+        <v>602032</v>
       </c>
       <c r="R39" t="n">
-        <v>6978478</v>
+        <v>6978549</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627818</v>
+        <v>129627873</v>
       </c>
       <c r="B13" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601994</v>
+        <v>602000</v>
       </c>
       <c r="R13" t="n">
-        <v>6978517</v>
+        <v>6978519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627873</v>
+        <v>129627818</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602000</v>
+        <v>601994</v>
       </c>
       <c r="R14" t="n">
-        <v>6978519</v>
+        <v>6978517</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627882</v>
+        <v>129627869</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602018</v>
+        <v>602056</v>
       </c>
       <c r="R16" t="n">
-        <v>6978681</v>
+        <v>6978555</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2114,11 +2114,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627869</v>
+        <v>129627882</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602056</v>
+        <v>602018</v>
       </c>
       <c r="R17" t="n">
-        <v>6978555</v>
+        <v>6978681</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2211,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627880</v>
+        <v>129627868</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601908</v>
+        <v>602022</v>
       </c>
       <c r="R20" t="n">
-        <v>6978584</v>
+        <v>6978574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2507,11 +2507,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627868</v>
+        <v>129627880</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602022</v>
+        <v>601908</v>
       </c>
       <c r="R21" t="n">
-        <v>6978574</v>
+        <v>6978584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2609,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627815</v>
+        <v>129627878</v>
       </c>
       <c r="B24" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>602026</v>
+        <v>601794</v>
       </c>
       <c r="R24" t="n">
-        <v>6978671</v>
+        <v>6978568</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129627878</v>
+        <v>129627815</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601794</v>
+        <v>602026</v>
       </c>
       <c r="R25" t="n">
-        <v>6978568</v>
+        <v>6978671</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627831</v>
+        <v>129627867</v>
       </c>
       <c r="B26" t="n">
-        <v>82916</v>
+        <v>97645</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601793</v>
+        <v>601979</v>
       </c>
       <c r="R26" t="n">
-        <v>6978563</v>
+        <v>6978701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627870</v>
+        <v>129627831</v>
       </c>
       <c r="B27" t="n">
-        <v>80186</v>
+        <v>82916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602039</v>
+        <v>601793</v>
       </c>
       <c r="R27" t="n">
-        <v>6978536</v>
+        <v>6978563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627871</v>
+        <v>129627870</v>
       </c>
       <c r="B28" t="n">
         <v>80186</v>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602019</v>
+        <v>602039</v>
       </c>
       <c r="R28" t="n">
-        <v>6978525</v>
+        <v>6978536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627825</v>
+        <v>129627871</v>
       </c>
       <c r="B29" t="n">
         <v>80186</v>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601965</v>
+        <v>602019</v>
       </c>
       <c r="R29" t="n">
-        <v>6978658</v>
+        <v>6978525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627819</v>
+        <v>129627825</v>
       </c>
       <c r="B30" t="n">
-        <v>80214</v>
+        <v>80186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601911</v>
+        <v>601965</v>
       </c>
       <c r="R30" t="n">
-        <v>6978481</v>
+        <v>6978658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627867</v>
+        <v>129627819</v>
       </c>
       <c r="B31" t="n">
-        <v>97645</v>
+        <v>80214</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601979</v>
+        <v>601911</v>
       </c>
       <c r="R31" t="n">
-        <v>6978701</v>
+        <v>6978481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,30 +3605,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B32" t="n">
-        <v>91613</v>
+        <v>97645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3636,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R32" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3672,11 +3676,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3703,34 +3702,30 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B33" t="n">
-        <v>97645</v>
+        <v>91613</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R33" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627865</v>
+        <v>129627872</v>
       </c>
       <c r="B5" t="n">
-        <v>97645</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601941</v>
+        <v>602013</v>
       </c>
       <c r="R5" t="n">
-        <v>6978598</v>
+        <v>6978512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627872</v>
+        <v>129627865</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>97645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602013</v>
+        <v>601941</v>
       </c>
       <c r="R6" t="n">
-        <v>6978512</v>
+        <v>6978598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627873</v>
+        <v>129627882</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602000</v>
+        <v>602018</v>
       </c>
       <c r="R13" t="n">
-        <v>6978519</v>
+        <v>6978681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627824</v>
+        <v>129627873</v>
       </c>
       <c r="B15" t="n">
         <v>80186</v>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601970</v>
+        <v>602000</v>
       </c>
       <c r="R15" t="n">
-        <v>6978601</v>
+        <v>6978519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627869</v>
+        <v>129627824</v>
       </c>
       <c r="B16" t="n">
         <v>80186</v>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602056</v>
+        <v>601970</v>
       </c>
       <c r="R16" t="n">
-        <v>6978555</v>
+        <v>6978601</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627882</v>
+        <v>129627869</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602018</v>
+        <v>602056</v>
       </c>
       <c r="R17" t="n">
-        <v>6978681</v>
+        <v>6978555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2211,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627823</v>
+        <v>129627880</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601951</v>
+        <v>601908</v>
       </c>
       <c r="R19" t="n">
-        <v>6978564</v>
+        <v>6978584</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2410,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,7 +2441,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627868</v>
+        <v>129627823</v>
       </c>
       <c r="B20" t="n">
         <v>80186</v>
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602022</v>
+        <v>601951</v>
       </c>
       <c r="R20" t="n">
-        <v>6978574</v>
+        <v>6978564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627880</v>
+        <v>129627868</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601908</v>
+        <v>602022</v>
       </c>
       <c r="R21" t="n">
-        <v>6978584</v>
+        <v>6978574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2604,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627878</v>
+        <v>129627815</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601794</v>
+        <v>602026</v>
       </c>
       <c r="R24" t="n">
-        <v>6978568</v>
+        <v>6978671</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129627815</v>
+        <v>129627878</v>
       </c>
       <c r="B25" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>602026</v>
+        <v>601794</v>
       </c>
       <c r="R25" t="n">
-        <v>6978671</v>
+        <v>6978568</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627867</v>
+        <v>129627831</v>
       </c>
       <c r="B26" t="n">
-        <v>97645</v>
+        <v>82916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601979</v>
+        <v>601793</v>
       </c>
       <c r="R26" t="n">
-        <v>6978701</v>
+        <v>6978563</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627831</v>
+        <v>129627870</v>
       </c>
       <c r="B27" t="n">
-        <v>82916</v>
+        <v>80186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601793</v>
+        <v>602039</v>
       </c>
       <c r="R27" t="n">
-        <v>6978563</v>
+        <v>6978536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627870</v>
+        <v>129627871</v>
       </c>
       <c r="B28" t="n">
         <v>80186</v>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602039</v>
+        <v>602019</v>
       </c>
       <c r="R28" t="n">
-        <v>6978536</v>
+        <v>6978525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627871</v>
+        <v>129627825</v>
       </c>
       <c r="B29" t="n">
         <v>80186</v>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602019</v>
+        <v>601965</v>
       </c>
       <c r="R29" t="n">
-        <v>6978525</v>
+        <v>6978658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627825</v>
+        <v>129627819</v>
       </c>
       <c r="B30" t="n">
-        <v>80186</v>
+        <v>80214</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601965</v>
+        <v>601911</v>
       </c>
       <c r="R30" t="n">
-        <v>6978658</v>
+        <v>6978481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627819</v>
+        <v>129627867</v>
       </c>
       <c r="B31" t="n">
-        <v>80214</v>
+        <v>97645</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601911</v>
+        <v>601979</v>
       </c>
       <c r="R31" t="n">
-        <v>6978481</v>
+        <v>6978701</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,34 +3605,30 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B32" t="n">
-        <v>97645</v>
+        <v>91613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3640,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R32" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,6 +3672,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3702,30 +3703,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B33" t="n">
-        <v>91613</v>
+        <v>97645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R33" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627826</v>
+        <v>129627834</v>
       </c>
       <c r="B34" t="n">
-        <v>80186</v>
+        <v>80221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601982</v>
+        <v>601971</v>
       </c>
       <c r="R34" t="n">
-        <v>6978637</v>
+        <v>6978654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627834</v>
+        <v>129627826</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601971</v>
+        <v>601982</v>
       </c>
       <c r="R35" t="n">
-        <v>6978654</v>
+        <v>6978637</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627817</v>
+        <v>129627879</v>
       </c>
       <c r="B36" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601963</v>
+        <v>601900</v>
       </c>
       <c r="R36" t="n">
-        <v>6978658</v>
+        <v>6978557</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4065,6 +4065,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4091,32 +4096,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627879</v>
+        <v>129627817</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601900</v>
+        <v>601963</v>
       </c>
       <c r="R37" t="n">
-        <v>6978557</v>
+        <v>6978658</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4162,11 +4167,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129627874</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627872</v>
+        <v>129627865</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>97649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602013</v>
+        <v>601941</v>
       </c>
       <c r="R5" t="n">
-        <v>6978512</v>
+        <v>6978598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627865</v>
+        <v>129627872</v>
       </c>
       <c r="B6" t="n">
-        <v>97645</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601941</v>
+        <v>602013</v>
       </c>
       <c r="R6" t="n">
-        <v>6978598</v>
+        <v>6978512</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627809</v>
+        <v>129627828</v>
       </c>
       <c r="B10" t="n">
-        <v>91557</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601974</v>
+        <v>602036</v>
       </c>
       <c r="R10" t="n">
-        <v>6978634</v>
+        <v>6978545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1553,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627828</v>
+        <v>129627809</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>91561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>602036</v>
+        <v>601974</v>
       </c>
       <c r="R11" t="n">
-        <v>6978545</v>
+        <v>6978634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1624,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627882</v>
+        <v>129627818</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602018</v>
+        <v>601994</v>
       </c>
       <c r="R13" t="n">
-        <v>6978681</v>
+        <v>6978517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627818</v>
+        <v>129627882</v>
       </c>
       <c r="B14" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601994</v>
+        <v>602018</v>
       </c>
       <c r="R14" t="n">
-        <v>6978517</v>
+        <v>6978681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627880</v>
+        <v>129627823</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601908</v>
+        <v>601951</v>
       </c>
       <c r="R19" t="n">
-        <v>6978584</v>
+        <v>6978564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2410,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2441,7 +2436,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627823</v>
+        <v>129627868</v>
       </c>
       <c r="B20" t="n">
         <v>80186</v>
@@ -2476,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601951</v>
+        <v>602022</v>
       </c>
       <c r="R20" t="n">
-        <v>6978564</v>
+        <v>6978574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627868</v>
+        <v>129627880</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602022</v>
+        <v>601908</v>
       </c>
       <c r="R21" t="n">
-        <v>6978574</v>
+        <v>6978584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2609,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2832,7 +2832,7 @@
         <v>129627815</v>
       </c>
       <c r="B24" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627831</v>
+        <v>129627867</v>
       </c>
       <c r="B26" t="n">
-        <v>82916</v>
+        <v>97649</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601793</v>
+        <v>601979</v>
       </c>
       <c r="R26" t="n">
-        <v>6978563</v>
+        <v>6978701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627867</v>
+        <v>129627831</v>
       </c>
       <c r="B31" t="n">
-        <v>97645</v>
+        <v>82916</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601979</v>
+        <v>601793</v>
       </c>
       <c r="R31" t="n">
-        <v>6978701</v>
+        <v>6978563</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,30 +3605,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B32" t="n">
-        <v>91613</v>
+        <v>97649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3636,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R32" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3672,11 +3676,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3703,34 +3702,30 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B33" t="n">
-        <v>97645</v>
+        <v>91617</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R33" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627834</v>
+        <v>129627826</v>
       </c>
       <c r="B34" t="n">
-        <v>80221</v>
+        <v>80186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601971</v>
+        <v>601982</v>
       </c>
       <c r="R34" t="n">
-        <v>6978654</v>
+        <v>6978637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627826</v>
+        <v>129627834</v>
       </c>
       <c r="B35" t="n">
-        <v>80186</v>
+        <v>80221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601982</v>
+        <v>601971</v>
       </c>
       <c r="R35" t="n">
-        <v>6978637</v>
+        <v>6978654</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627879</v>
+        <v>129627817</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601900</v>
+        <v>601963</v>
       </c>
       <c r="R36" t="n">
-        <v>6978557</v>
+        <v>6978658</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4065,11 +4065,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627817</v>
+        <v>129627827</v>
       </c>
       <c r="B37" t="n">
-        <v>80215</v>
+        <v>98778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4131,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601963</v>
+        <v>602032</v>
       </c>
       <c r="R37" t="n">
-        <v>6978658</v>
+        <v>6978549</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,6 +4162,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627863</v>
+        <v>129627879</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601836</v>
+        <v>601900</v>
       </c>
       <c r="R38" t="n">
-        <v>6978478</v>
+        <v>6978557</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4295,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627827</v>
+        <v>129627863</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602032</v>
+        <v>601836</v>
       </c>
       <c r="R39" t="n">
-        <v>6978549</v>
+        <v>6978478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4706,7 @@
         <v>129627808</v>
       </c>
       <c r="B43" t="n">
-        <v>91817</v>
+        <v>91821</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129627874</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627865</v>
+        <v>129627872</v>
       </c>
       <c r="B5" t="n">
-        <v>97649</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601941</v>
+        <v>602013</v>
       </c>
       <c r="R5" t="n">
-        <v>6978598</v>
+        <v>6978512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627872</v>
+        <v>129627865</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>97651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602013</v>
+        <v>601941</v>
       </c>
       <c r="R6" t="n">
-        <v>6978512</v>
+        <v>6978598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>129627830</v>
       </c>
       <c r="B7" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627828</v>
+        <v>129627809</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>91563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602036</v>
+        <v>601974</v>
       </c>
       <c r="R10" t="n">
-        <v>6978545</v>
+        <v>6978634</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627809</v>
+        <v>129627828</v>
       </c>
       <c r="B11" t="n">
-        <v>91561</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601974</v>
+        <v>602036</v>
       </c>
       <c r="R11" t="n">
-        <v>6978634</v>
+        <v>6978545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627818</v>
+        <v>129627882</v>
       </c>
       <c r="B13" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601994</v>
+        <v>602018</v>
       </c>
       <c r="R13" t="n">
-        <v>6978517</v>
+        <v>6978681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627882</v>
+        <v>129627873</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602018</v>
+        <v>602000</v>
       </c>
       <c r="R14" t="n">
-        <v>6978681</v>
+        <v>6978519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627873</v>
+        <v>129627818</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602000</v>
+        <v>601994</v>
       </c>
       <c r="R15" t="n">
-        <v>6978519</v>
+        <v>6978517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627823</v>
+        <v>129627880</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601951</v>
+        <v>601908</v>
       </c>
       <c r="R19" t="n">
-        <v>6978564</v>
+        <v>6978584</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2410,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,7 +2441,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627868</v>
+        <v>129627823</v>
       </c>
       <c r="B20" t="n">
         <v>80186</v>
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602022</v>
+        <v>601951</v>
       </c>
       <c r="R20" t="n">
-        <v>6978574</v>
+        <v>6978564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627880</v>
+        <v>129627868</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601908</v>
+        <v>602022</v>
       </c>
       <c r="R21" t="n">
-        <v>6978584</v>
+        <v>6978574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2604,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627815</v>
+        <v>129627878</v>
       </c>
       <c r="B24" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>602026</v>
+        <v>601794</v>
       </c>
       <c r="R24" t="n">
-        <v>6978671</v>
+        <v>6978568</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129627878</v>
+        <v>129627815</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601794</v>
+        <v>602026</v>
       </c>
       <c r="R25" t="n">
-        <v>6978568</v>
+        <v>6978671</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627867</v>
+        <v>129627831</v>
       </c>
       <c r="B26" t="n">
-        <v>97649</v>
+        <v>82918</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601979</v>
+        <v>601793</v>
       </c>
       <c r="R26" t="n">
-        <v>6978701</v>
+        <v>6978563</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627831</v>
+        <v>129627867</v>
       </c>
       <c r="B31" t="n">
-        <v>82916</v>
+        <v>97651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601793</v>
+        <v>601979</v>
       </c>
       <c r="R31" t="n">
-        <v>6978563</v>
+        <v>6978701</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,7 +3608,7 @@
         <v>129627864</v>
       </c>
       <c r="B32" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>129627875</v>
       </c>
       <c r="B33" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627817</v>
+        <v>129627863</v>
       </c>
       <c r="B36" t="n">
-        <v>80215</v>
+        <v>57896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601963</v>
+        <v>601836</v>
       </c>
       <c r="R36" t="n">
-        <v>6978658</v>
+        <v>6978478</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4065,6 +4065,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4094,7 +4099,7 @@
         <v>129627827</v>
       </c>
       <c r="B37" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>80215</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R39" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,11 +4371,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4706,7 @@
         <v>129627808</v>
       </c>
       <c r="B43" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627882</v>
+        <v>129627873</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602018</v>
+        <v>602000</v>
       </c>
       <c r="R13" t="n">
-        <v>6978681</v>
+        <v>6978519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627873</v>
+        <v>129627818</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602000</v>
+        <v>601994</v>
       </c>
       <c r="R14" t="n">
-        <v>6978519</v>
+        <v>6978517</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627818</v>
+        <v>129627824</v>
       </c>
       <c r="B15" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601994</v>
+        <v>601970</v>
       </c>
       <c r="R15" t="n">
-        <v>6978517</v>
+        <v>6978601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627824</v>
+        <v>129627869</v>
       </c>
       <c r="B16" t="n">
         <v>80186</v>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601970</v>
+        <v>602056</v>
       </c>
       <c r="R16" t="n">
-        <v>6978601</v>
+        <v>6978555</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627869</v>
+        <v>129627882</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602056</v>
+        <v>602018</v>
       </c>
       <c r="R17" t="n">
-        <v>6978555</v>
+        <v>6978681</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2211,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627873</v>
+        <v>129627882</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602000</v>
+        <v>602018</v>
       </c>
       <c r="R13" t="n">
-        <v>6978519</v>
+        <v>6978681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627818</v>
+        <v>129627873</v>
       </c>
       <c r="B14" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601994</v>
+        <v>602000</v>
       </c>
       <c r="R14" t="n">
-        <v>6978517</v>
+        <v>6978519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627824</v>
+        <v>129627818</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601970</v>
+        <v>601994</v>
       </c>
       <c r="R15" t="n">
-        <v>6978601</v>
+        <v>6978517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627869</v>
+        <v>129627824</v>
       </c>
       <c r="B16" t="n">
         <v>80186</v>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602056</v>
+        <v>601970</v>
       </c>
       <c r="R16" t="n">
-        <v>6978555</v>
+        <v>6978601</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627882</v>
+        <v>129627869</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602018</v>
+        <v>602056</v>
       </c>
       <c r="R17" t="n">
-        <v>6978681</v>
+        <v>6978555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2211,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B36" t="n">
-        <v>57896</v>
+        <v>80215</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R36" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4065,11 +4065,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4300,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627817</v>
+        <v>129627863</v>
       </c>
       <c r="B39" t="n">
-        <v>80215</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601963</v>
+        <v>601836</v>
       </c>
       <c r="R39" t="n">
-        <v>6978658</v>
+        <v>6978478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,6 +4366,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627817</v>
+        <v>129627863</v>
       </c>
       <c r="B36" t="n">
-        <v>80215</v>
+        <v>57896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601963</v>
+        <v>601836</v>
       </c>
       <c r="R36" t="n">
-        <v>6978658</v>
+        <v>6978478</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4065,6 +4065,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4295,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>80215</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R39" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,11 +4371,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129627874</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129627865</v>
       </c>
       <c r="B6" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>129627828</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627831</v>
+        <v>129627870</v>
       </c>
       <c r="B26" t="n">
-        <v>82918</v>
+        <v>80186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601793</v>
+        <v>602039</v>
       </c>
       <c r="R26" t="n">
-        <v>6978563</v>
+        <v>6978536</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627870</v>
+        <v>129627871</v>
       </c>
       <c r="B27" t="n">
         <v>80186</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602039</v>
+        <v>602019</v>
       </c>
       <c r="R27" t="n">
-        <v>6978536</v>
+        <v>6978525</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627871</v>
+        <v>129627825</v>
       </c>
       <c r="B28" t="n">
         <v>80186</v>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602019</v>
+        <v>601965</v>
       </c>
       <c r="R28" t="n">
-        <v>6978525</v>
+        <v>6978658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,32 +3314,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627825</v>
+        <v>129627819</v>
       </c>
       <c r="B29" t="n">
-        <v>80186</v>
+        <v>80214</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601965</v>
+        <v>601911</v>
       </c>
       <c r="R29" t="n">
-        <v>6978658</v>
+        <v>6978481</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627819</v>
+        <v>129627831</v>
       </c>
       <c r="B30" t="n">
-        <v>80214</v>
+        <v>82918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601911</v>
+        <v>601793</v>
       </c>
       <c r="R30" t="n">
-        <v>6978481</v>
+        <v>6978563</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3511,7 +3511,7 @@
         <v>129627867</v>
       </c>
       <c r="B31" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,34 +3605,30 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B32" t="n">
-        <v>97651</v>
+        <v>91619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3640,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R32" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,6 +3672,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3702,30 +3703,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B33" t="n">
-        <v>91619</v>
+        <v>97661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R33" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,7 +4099,7 @@
         <v>129627827</v>
       </c>
       <c r="B37" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627872</v>
+        <v>129627865</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>97661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602013</v>
+        <v>601941</v>
       </c>
       <c r="R5" t="n">
-        <v>6978512</v>
+        <v>6978598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627865</v>
+        <v>129627872</v>
       </c>
       <c r="B6" t="n">
-        <v>97661</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601941</v>
+        <v>602013</v>
       </c>
       <c r="R6" t="n">
-        <v>6978598</v>
+        <v>6978512</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3605,30 +3605,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B32" t="n">
-        <v>91619</v>
+        <v>97661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3636,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R32" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3672,11 +3676,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3703,34 +3702,30 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B33" t="n">
-        <v>97661</v>
+        <v>91619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R33" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627863</v>
+        <v>129627879</v>
       </c>
       <c r="B36" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601836</v>
+        <v>601900</v>
       </c>
       <c r="R36" t="n">
-        <v>6978478</v>
+        <v>6978557</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,32 +4096,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627827</v>
+        <v>129627863</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602032</v>
+        <v>601836</v>
       </c>
       <c r="R37" t="n">
-        <v>6978549</v>
+        <v>6978478</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627879</v>
+        <v>129627817</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601900</v>
+        <v>601963</v>
       </c>
       <c r="R38" t="n">
-        <v>6978557</v>
+        <v>6978658</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,11 +4269,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4300,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627817</v>
+        <v>129627827</v>
       </c>
       <c r="B39" t="n">
-        <v>80215</v>
+        <v>98790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601963</v>
+        <v>602032</v>
       </c>
       <c r="R39" t="n">
-        <v>6978658</v>
+        <v>6978549</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,6 +4366,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129627865</v>
+        <v>129627872</v>
       </c>
       <c r="B5" t="n">
-        <v>97661</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601941</v>
+        <v>602013</v>
       </c>
       <c r="R5" t="n">
-        <v>6978598</v>
+        <v>6978512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627872</v>
+        <v>129627865</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>97661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602013</v>
+        <v>601941</v>
       </c>
       <c r="R6" t="n">
-        <v>6978512</v>
+        <v>6978598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B7" t="n">
-        <v>82918</v>
+        <v>80215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R7" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B8" t="n">
-        <v>80215</v>
+        <v>82918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R8" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
         <v>129627810</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>129627859</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>129627814</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129627808</v>
       </c>
       <c r="B43" t="n">
-        <v>91823</v>
+        <v>91826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627877</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129627881</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129627874</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129627872</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129627865</v>
       </c>
       <c r="B6" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B7" t="n">
-        <v>80215</v>
+        <v>82921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R7" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B8" t="n">
-        <v>82918</v>
+        <v>80218</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R8" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>129627822</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129627809</v>
       </c>
       <c r="B10" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>129627828</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129627820</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627882</v>
+        <v>129627873</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602018</v>
+        <v>602000</v>
       </c>
       <c r="R13" t="n">
-        <v>6978681</v>
+        <v>6978519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627873</v>
+        <v>129627818</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>80218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602000</v>
+        <v>601994</v>
       </c>
       <c r="R14" t="n">
-        <v>6978519</v>
+        <v>6978517</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627818</v>
+        <v>129627824</v>
       </c>
       <c r="B15" t="n">
-        <v>80215</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601994</v>
+        <v>601970</v>
       </c>
       <c r="R15" t="n">
-        <v>6978517</v>
+        <v>6978601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627824</v>
+        <v>129627869</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601970</v>
+        <v>602056</v>
       </c>
       <c r="R16" t="n">
-        <v>6978601</v>
+        <v>6978555</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627869</v>
+        <v>129627882</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602056</v>
+        <v>602018</v>
       </c>
       <c r="R17" t="n">
-        <v>6978555</v>
+        <v>6978681</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2211,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2245,7 +2245,7 @@
         <v>129627829</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>129627880</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>129627823</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129627868</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129627876</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>129627832</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129627878</v>
+        <v>129627815</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>91623</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601794</v>
+        <v>602026</v>
       </c>
       <c r="R24" t="n">
-        <v>6978568</v>
+        <v>6978671</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129627815</v>
+        <v>129627878</v>
       </c>
       <c r="B25" t="n">
-        <v>91620</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>602026</v>
+        <v>601794</v>
       </c>
       <c r="R25" t="n">
-        <v>6978671</v>
+        <v>6978568</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627870</v>
+        <v>129627831</v>
       </c>
       <c r="B26" t="n">
-        <v>80186</v>
+        <v>82921</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602039</v>
+        <v>601793</v>
       </c>
       <c r="R26" t="n">
-        <v>6978536</v>
+        <v>6978563</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627871</v>
+        <v>129627870</v>
       </c>
       <c r="B27" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602019</v>
+        <v>602039</v>
       </c>
       <c r="R27" t="n">
-        <v>6978525</v>
+        <v>6978536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>129627825</v>
       </c>
       <c r="B28" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3314,32 +3314,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627819</v>
+        <v>129627871</v>
       </c>
       <c r="B29" t="n">
-        <v>80214</v>
+        <v>80189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601911</v>
+        <v>602019</v>
       </c>
       <c r="R29" t="n">
-        <v>6978481</v>
+        <v>6978525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627831</v>
+        <v>129627819</v>
       </c>
       <c r="B30" t="n">
-        <v>82918</v>
+        <v>80217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601793</v>
+        <v>601911</v>
       </c>
       <c r="R30" t="n">
-        <v>6978563</v>
+        <v>6978481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3511,7 +3511,7 @@
         <v>129627867</v>
       </c>
       <c r="B31" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,34 +3605,30 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627864</v>
+        <v>129627875</v>
       </c>
       <c r="B32" t="n">
-        <v>97661</v>
+        <v>91622</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3640,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602045</v>
+        <v>601812</v>
       </c>
       <c r="R32" t="n">
-        <v>6978541</v>
+        <v>6978576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,6 +3672,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3702,30 +3703,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627875</v>
+        <v>129627864</v>
       </c>
       <c r="B33" t="n">
-        <v>91619</v>
+        <v>97665</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601812</v>
+        <v>602045</v>
       </c>
       <c r="R33" t="n">
-        <v>6978576</v>
+        <v>6978541</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627826</v>
+        <v>129627834</v>
       </c>
       <c r="B34" t="n">
-        <v>80186</v>
+        <v>80224</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601982</v>
+        <v>601971</v>
       </c>
       <c r="R34" t="n">
-        <v>6978637</v>
+        <v>6978654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627834</v>
+        <v>129627826</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>80189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601971</v>
+        <v>601982</v>
       </c>
       <c r="R35" t="n">
-        <v>6978654</v>
+        <v>6978637</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
         <v>129627879</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4096,32 +4096,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627863</v>
+        <v>129627817</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>80218</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601836</v>
+        <v>601963</v>
       </c>
       <c r="R37" t="n">
-        <v>6978478</v>
+        <v>6978658</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,11 +4167,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4198,32 +4193,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627817</v>
+        <v>129627863</v>
       </c>
       <c r="B38" t="n">
-        <v>80215</v>
+        <v>57895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601963</v>
+        <v>601836</v>
       </c>
       <c r="R38" t="n">
-        <v>6978658</v>
+        <v>6978478</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,6 +4264,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4298,7 +4298,7 @@
         <v>129627827</v>
       </c>
       <c r="B39" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49754-2025 artfynd.xlsx
+++ b/artfynd/A 49754-2025 artfynd.xlsx
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627830</v>
+        <v>129627816</v>
       </c>
       <c r="B7" t="n">
-        <v>82921</v>
+        <v>80218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601964</v>
+        <v>602018</v>
       </c>
       <c r="R7" t="n">
-        <v>6978529</v>
+        <v>6978523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627816</v>
+        <v>129627830</v>
       </c>
       <c r="B8" t="n">
-        <v>80218</v>
+        <v>82921</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602018</v>
+        <v>601964</v>
       </c>
       <c r="R8" t="n">
-        <v>6978523</v>
+        <v>6978529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627873</v>
+        <v>129627882</v>
       </c>
       <c r="B13" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602000</v>
+        <v>602018</v>
       </c>
       <c r="R13" t="n">
-        <v>6978519</v>
+        <v>6978681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627818</v>
+        <v>129627873</v>
       </c>
       <c r="B14" t="n">
-        <v>80218</v>
+        <v>80189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601994</v>
+        <v>602000</v>
       </c>
       <c r="R14" t="n">
-        <v>6978517</v>
+        <v>6978519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627824</v>
+        <v>129627818</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>80218</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601970</v>
+        <v>601994</v>
       </c>
       <c r="R15" t="n">
-        <v>6978601</v>
+        <v>6978517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627869</v>
+        <v>129627824</v>
       </c>
       <c r="B16" t="n">
         <v>80189</v>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602056</v>
+        <v>601970</v>
       </c>
       <c r="R16" t="n">
-        <v>6978555</v>
+        <v>6978601</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627882</v>
+        <v>129627869</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602018</v>
+        <v>602056</v>
       </c>
       <c r="R17" t="n">
-        <v>6978681</v>
+        <v>6978555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2211,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129627831</v>
+        <v>129627870</v>
       </c>
       <c r="B26" t="n">
-        <v>82921</v>
+        <v>80189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601793</v>
+        <v>602039</v>
       </c>
       <c r="R26" t="n">
-        <v>6978563</v>
+        <v>6978536</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129627870</v>
+        <v>129627825</v>
       </c>
       <c r="B27" t="n">
         <v>80189</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602039</v>
+        <v>601965</v>
       </c>
       <c r="R27" t="n">
-        <v>6978536</v>
+        <v>6978658</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129627825</v>
+        <v>129627867</v>
       </c>
       <c r="B28" t="n">
-        <v>80189</v>
+        <v>97665</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601965</v>
+        <v>601979</v>
       </c>
       <c r="R28" t="n">
-        <v>6978658</v>
+        <v>6978701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627871</v>
+        <v>129627831</v>
       </c>
       <c r="B29" t="n">
-        <v>80189</v>
+        <v>82921</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602019</v>
+        <v>601793</v>
       </c>
       <c r="R29" t="n">
-        <v>6978525</v>
+        <v>6978563</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627819</v>
+        <v>129627871</v>
       </c>
       <c r="B30" t="n">
-        <v>80217</v>
+        <v>80189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601911</v>
+        <v>602019</v>
       </c>
       <c r="R30" t="n">
-        <v>6978481</v>
+        <v>6978525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627867</v>
+        <v>129627819</v>
       </c>
       <c r="B31" t="n">
-        <v>97665</v>
+        <v>80217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601979</v>
+        <v>601911</v>
       </c>
       <c r="R31" t="n">
-        <v>6978701</v>
+        <v>6978481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627879</v>
+        <v>129627863</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>57895</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601900</v>
+        <v>601836</v>
       </c>
       <c r="R36" t="n">
-        <v>6978557</v>
+        <v>6978478</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>2 ex, övriga läten/lockläten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627863</v>
+        <v>129627879</v>
       </c>
       <c r="B38" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601836</v>
+        <v>601900</v>
       </c>
       <c r="R38" t="n">
-        <v>6978478</v>
+        <v>6978557</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 ex, övriga läten/lockläten</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
